--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104588_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104588_W15.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0781</v>
+        <v>5.9466</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4013</v>
+        <v>8.1015</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3231</v>
+        <v>-2.1548</v>
       </c>
       <c r="G2" t="n">
-        <v>3.048</v>
+        <v>3.0344</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1444</v>
+        <v>2.1318</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9036</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5891</v>
+        <v>5.543</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1764</v>
+        <v>4.1434</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.541</v>
+        <v>-2.5086</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.032</v>
+        <v>-2.0116</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8703</v>
+        <v>-0.971</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7289</v>
+        <v>0.0507</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1414</v>
+        <v>-1.0217</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8077</v>
+        <v>4.7937</v>
       </c>
       <c r="W2" t="n">
-        <v>6.1704</v>
+        <v>6.1499</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9726</v>
+        <v>3.8308</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7693</v>
+        <v>3.3478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2033</v>
+        <v>0.483</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1286</v>
+        <v>3.1321</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9393</v>
+        <v>2.9382</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1893</v>
+        <v>0.1939</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2316</v>
+        <v>3.2171</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0824</v>
+        <v>3.0682</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.103</v>
+        <v>-0.0851</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1881</v>
+        <v>0.037</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9648</v>
+        <v>0.5664</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.5294</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.445</v>
+        <v>2.2273</v>
       </c>
       <c r="E4" t="n">
-        <v>1.408</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.037</v>
+        <v>1.3004</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5545</v>
+        <v>2.6466</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2613</v>
+        <v>-0.4826</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2932</v>
+        <v>3.1292</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4911</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2353</v>
+        <v>0.696</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2558</v>
+        <v>2.554</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0457</v>
+        <v>-0.6034</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4966</v>
+        <v>-1.1786</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.549</v>
+        <v>0.5752</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4025</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>0.597</v>
+        <v>-1.0535</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7561</v>
+        <v>0.0019</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1591</v>
+        <v>-1.0554</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.96</v>
+        <v>1.3612</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9478</v>
+        <v>3.4479</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9878</v>
+        <v>-2.0867</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.354</v>
+        <v>-0.3438</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4979</v>
+        <v>-0.4915</v>
       </c>
       <c r="I5" t="n">
-        <v>0.144</v>
+        <v>0.1476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9563</v>
+        <v>0.9465</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3103</v>
+        <v>-1.2904</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1948</v>
+        <v>-0.4041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5263</v>
+        <v>0.0556</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3315</v>
+        <v>-0.4596</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4349</v>
+        <v>1.3146</v>
       </c>
       <c r="E6" t="n">
-        <v>0.383</v>
+        <v>0.6811</v>
       </c>
       <c r="F6" t="n">
-        <v>1.052</v>
+        <v>0.6335</v>
       </c>
       <c r="G6" t="n">
-        <v>2.655</v>
+        <v>-1.5493</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4849</v>
+        <v>-1.2527</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1399</v>
+        <v>-0.2966</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2825</v>
+        <v>0.4727</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7131</v>
+        <v>0.2273</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5694</v>
+        <v>0.2453</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-2.0219</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.198</v>
+        <v>-1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5705</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>3.4145</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9488</v>
+        <v>3.4145</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8591</v>
+        <v>-0.5506</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5898</v>
+        <v>0.0507</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2694</v>
+        <v>-0.6012</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2159</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1875</v>
+        <v>1.9227</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9716</v>
+        <v>-1.0643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3046</v>
+        <v>-0.2963</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7008</v>
+        <v>1.6632</v>
       </c>
       <c r="K7" t="n">
-        <v>0.107</v>
+        <v>0.0927</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5938</v>
+        <v>1.5705</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7447</v>
+        <v>-0.7164</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2207</v>
+        <v>-0.5713</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6079</v>
+        <v>0.1716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6128</v>
+        <v>-0.7428</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.8829</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1663</v>
+        <v>-0.1655</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0588</v>
+        <v>-0.4783</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2252</v>
+        <v>0.3128</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9465</v>
+        <v>-0.9347</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5413</v>
+        <v>-0.5264</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4052</v>
+        <v>-0.4083</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8945</v>
+        <v>-0.9077</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0521</v>
+        <v>-0.027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5831</v>
+        <v>0.244</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1039</v>
+        <v>0.7058</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5208</v>
+        <v>-0.4618</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4254</v>
+        <v>-0.2649</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0522</v>
+        <v>-2.0349</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3732</v>
+        <v>1.7701</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3559</v>
+        <v>-0.5321</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0173</v>
+        <v>-0.0494</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3732</v>
+        <v>-0.4828</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0173</v>
+        <v>-1.3786</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>-0.7379</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6407</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3732</v>
+        <v>0.8465</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.6886</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3732</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0696</v>
+        <v>-0.5051</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.0629</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.4422</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>G. FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7166</v>
+        <v>-0.3064</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3767</v>
+        <v>0.066</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6601</v>
+        <v>-0.3724</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5391</v>
+        <v>-0.3551</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0593</v>
+        <v>0.0172</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4798</v>
+        <v>-0.3724</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3715</v>
+        <v>0.0172</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6371</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8324</v>
+        <v>-0.3724</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6751</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>-0.3724</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9506</v>
+        <v>0.0487</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>0.0487</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5332</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5484</v>
+        <v>-2.8104</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0403</v>
+        <v>-1.2859</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.508</v>
+        <v>-1.5245</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7328</v>
+        <v>-0.7281</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6075</v>
+        <v>-0.6061</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1253</v>
+        <v>-0.122</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0483</v>
+        <v>-0.0546</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6844</v>
+        <v>-0.6734</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0668</v>
+        <v>-0.2009</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9149</v>
+        <v>-4.0871</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1562</v>
+        <v>-1.2209</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7587</v>
+        <v>-2.8662</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1763</v>
+        <v>-0.1524</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4806</v>
+        <v>-0.1318</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6957</v>
+        <v>-0.0206</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6342</v>
+        <v>1.1207</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3303</v>
+        <v>-0.1454</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3039</v>
+        <v>1.2661</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.542</v>
+        <v>-1.2731</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1503</v>
+        <v>0.0135</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3918</v>
+        <v>-1.2866</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1757</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.007</v>
+        <v>-0.281</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0393</v>
+        <v>0.1623</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0463</v>
+        <v>-0.4433</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-2.2879</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3462</v>
+        <v>-4.2391</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2609</v>
+        <v>-3.302</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0854</v>
+        <v>-0.9371</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1535</v>
+        <v>-3.1705</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1269</v>
+        <v>-2.4733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0266</v>
+        <v>-0.6972</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1436</v>
+        <v>-1.6512</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1252</v>
+        <v>-1.338</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2688</v>
+        <v>-0.3132</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2971</v>
+        <v>-1.5193</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0017</v>
+        <v>-1.1353</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2954</v>
+        <v>-0.384</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>3.1868</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5371</v>
+        <v>-0.345</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0907</v>
+        <v>-0.077</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6279</v>
+        <v>-0.268</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2946</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2946</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.321300000000001</v>
+        <v>3.6655</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1518</v>
+        <v>10.1719</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.8302</v>
+        <v>-6.506200000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9751</v>
+        <v>1.9939</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.263299999999999</v>
+        <v>-1.222899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2385</v>
+        <v>3.2165</v>
       </c>
       <c r="J14" t="n">
-        <v>12.4638</v>
+        <v>12.2383</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6008</v>
+        <v>5.464399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8631</v>
+        <v>6.7737</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.4886</v>
+        <v>-10.2445</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.864100000000001</v>
+        <v>-6.6873</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.6245</v>
+        <v>-3.5573</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4024</v>
+        <v>3.4144</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5491</v>
+        <v>21.625</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.884599999999999</v>
+        <v>-4.5528</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4365</v>
+        <v>1.8083</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.3212</v>
+        <v>-6.360899999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>2.828200000000001</v>
+        <v>2.809999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>14.3978</v>
+        <v>14.3359</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.5696</v>
+        <v>-11.5257</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0329</v>
+        <v>2.6933</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6215</v>
+        <v>3.7073</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5886</v>
+        <v>-1.014</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4836</v>
+        <v>4.4849</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8225</v>
+        <v>3.8173</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6611</v>
+        <v>0.6676</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8075</v>
+        <v>4.7857</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6582</v>
+        <v>4.6367</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3239</v>
+        <v>-0.3007</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9256</v>
+        <v>1.5782</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3753</v>
+        <v>1.4954</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4497</v>
+        <v>0.0827</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.1494</v>
+        <v>-3.1422</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.3102</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3714</v>
+        <v>2.3444</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9179</v>
+        <v>2.536</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5466</v>
+        <v>-0.1916</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.649</v>
+        <v>0.6439</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2785</v>
+        <v>-0.4193</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9275</v>
+        <v>1.0632</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8321</v>
+        <v>0.8276</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7202</v>
+        <v>-0.3038</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>1.1313</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4812</v>
+        <v>-0.1836</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4417</v>
+        <v>-0.1155</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0395</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3664</v>
+        <v>0.3937</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0858</v>
+        <v>0.6268</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2806</v>
+        <v>-0.2331</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7071</v>
+        <v>1.9896</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>-1.8235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8777</v>
+        <v>1.1082</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9361</v>
+        <v>1.8416</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0584</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5599</v>
+        <v>1.0048</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9539</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.394</v>
+        <v>0.1001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1748</v>
+        <v>0.7872</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1748</v>
+        <v>0.6755</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6149</v>
+        <v>0.2176</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2209</v>
+        <v>0.2292</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.394</v>
+        <v>-0.0116</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3327</v>
+        <v>0.2927</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2299</v>
+        <v>0.4202</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1028</v>
+        <v>-0.1275</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7997</v>
+        <v>-0.1893</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8015</v>
+        <v>1.067</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4033</v>
+        <v>1.6761</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6018</v>
+        <v>-0.6092</v>
       </c>
       <c r="G18" t="n">
-        <v>0.653</v>
+        <v>-0.637</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4184</v>
+        <v>0.2786</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0715</v>
+        <v>-0.9156</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8217</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2913</v>
+        <v>0.71</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1487</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2044</v>
+        <v>-1.4587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1272</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0772</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1635</v>
+        <v>1.0407</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5565</v>
+        <v>0.8545</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.607</v>
+        <v>0.1862</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9925</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>3.8243</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8319</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.634</v>
+        <v>0.5041</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7359</v>
+        <v>1.5502</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1019</v>
+        <v>-1.0461</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9981</v>
+        <v>0.5541</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9046999999999999</v>
+        <v>1.9422</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09329999999999999</v>
+        <v>-1.3881</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7975</v>
+        <v>2.1579</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6856</v>
+        <v>2.1579</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2006</v>
+        <v>-1.6037</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2192</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0186</v>
+        <v>-1.3881</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1712</v>
+        <v>-0.021</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>-0.1233</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4706</v>
+        <v>0.1024</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1929</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2527</v>
+        <v>0.0362</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1721</v>
+        <v>-0.3308</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4248</v>
+        <v>0.367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1845</v>
+        <v>1.7483</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5629</v>
+        <v>0.7416</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3785</v>
+        <v>1.0067</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7385</v>
+        <v>2.0202</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.2163</v>
       </c>
       <c r="L20" t="n">
-        <v>0.112</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.554</v>
+        <v>-0.2719</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>-0.4747</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>0.2028</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.8697</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4336</v>
+        <v>0.2715</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.2755</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7997</v>
+        <v>-1.121</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-2.3683</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5489000000000001</v>
+        <v>0.0348</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0944</v>
+        <v>1.2271</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6433</v>
+        <v>-1.1923</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7508</v>
+        <v>-1.7585</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1053</v>
+        <v>-2.1052</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3545</v>
+        <v>0.3467</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9425</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7659</v>
+        <v>-0.7831</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7085</v>
+        <v>1.6899</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6933</v>
+        <v>-2.6653</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2946</v>
+        <v>0.8827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>0.4177</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0597</v>
+        <v>0.465</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9102</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8225</v>
+        <v>-0.591</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0877</v>
+        <v>-0.0516</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2505</v>
+        <v>-0.2489</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0346</v>
+        <v>-0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5622</v>
+        <v>-0.5592</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0209</v>
+        <v>0.2892</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.2369</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1191</v>
+        <v>-0.681</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1009</v>
+        <v>1.5692</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0182</v>
+        <v>-2.2502</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7663</v>
+        <v>0.1784</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7534</v>
+        <v>0.552</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0129</v>
+        <v>-0.3737</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0584</v>
+        <v>0.7215</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2428</v>
+        <v>0.6098</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8156</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2921</v>
+        <v>-0.5432</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1973</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6264</v>
+        <v>0.4773</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>0.8476</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0699</v>
+        <v>-0.3703</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1248</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3782</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2276</v>
+        <v>-1.9338</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1864</v>
+        <v>-1.0811</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0412</v>
+        <v>-0.8527</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.524</v>
+        <v>-3.5075</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7679</v>
+        <v>-0.7533</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7561</v>
+        <v>-2.7542</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2356</v>
+        <v>-1.2435</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2251</v>
+        <v>0.2241</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2884</v>
+        <v>-2.264</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0696</v>
+        <v>0.3461</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0907</v>
+        <v>0.2111</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0212</v>
+        <v>0.135</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6053</v>
+        <v>-2.9957</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3299</v>
+        <v>-1.4085</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7247</v>
+        <v>-1.5872</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5083</v>
+        <v>0.0599</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3115</v>
+        <v>-0.3843</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1968</v>
+        <v>0.4442</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4967</v>
+        <v>1.6765</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.633</v>
+        <v>-0.1109</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8637</v>
+        <v>1.7874</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0116</v>
+        <v>-1.6166</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6785</v>
+        <v>-0.2734</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3331</v>
+        <v>-1.3432</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6805</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4154</v>
+        <v>-0.0964</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5939</v>
+        <v>0.3295</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1785</v>
+        <v>-0.4259</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1929</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.3751</v>
+        <v>-3.2725</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6111</v>
+        <v>-4.1898</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.764</v>
+        <v>0.9174</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0622</v>
+        <v>-4.5162</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.375</v>
+        <v>-3.317</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4372</v>
+        <v>-1.1992</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7006</v>
+        <v>-3.5272</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0906</v>
+        <v>-2.6554</v>
       </c>
       <c r="L26" t="n">
-        <v>1.7912</v>
+        <v>-0.8718</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.6384</v>
+        <v>-0.989</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2844</v>
+        <v>-0.6615</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.354</v>
+        <v>-0.3275</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.9488</v>
+        <v>0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4025</v>
+        <v>-1.5934</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4884</v>
+        <v>0.7502</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0907</v>
+        <v>0.7731</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5792</v>
+        <v>-0.0229</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.1893</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.3471</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.321400000000001</v>
+        <v>-1.7376</v>
       </c>
       <c r="E27" t="n">
-        <v>6.830399999999999</v>
+        <v>6.5063</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.1518</v>
+        <v>-8.243899999999998</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.975</v>
+        <v>-1.993800000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2632</v>
+        <v>1.222799999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.2383</v>
+        <v>-3.2167</v>
       </c>
       <c r="J27" t="n">
-        <v>10.4887</v>
+        <v>10.2447</v>
       </c>
       <c r="K27" t="n">
-        <v>6.8641</v>
+        <v>6.6874</v>
       </c>
       <c r="L27" t="n">
-        <v>3.6248</v>
+        <v>3.5571</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.4638</v>
+        <v>-12.2383</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.6008</v>
+        <v>-5.464399999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.863</v>
+        <v>-6.773899999999998</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q27" t="n">
-        <v>-21.5492</v>
+        <v>-21.6251</v>
       </c>
       <c r="R27" t="n">
-        <v>18.1469</v>
+        <v>18.2107</v>
       </c>
       <c r="S27" t="n">
-        <v>4.884499999999999</v>
+        <v>6.480399999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>6.321100000000001</v>
+        <v>6.361000000000002</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4368</v>
+        <v>0.1194</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.8283</v>
+        <v>-2.81</v>
       </c>
       <c r="W27" t="n">
-        <v>11.5695</v>
+        <v>11.5259</v>
       </c>
       <c r="X27" t="n">
-        <v>-14.3978</v>
+        <v>-14.3358</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104588_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104588_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.5257</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-3.3</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.8235</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2788</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.3683</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.3471</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104588_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-14.3358</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
